--- a/Documents/uno_q_pin_info.xlsx
+++ b/Documents/uno_q_pin_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_UNO_Q\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_UNO_Q\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BE6C7C-AF20-4FE0-8D89-DD76E31E03BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044E281D-BB9A-46B6-B865-6BB9B19C1396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="1230" windowWidth="25020" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
+    <workbookView xWindow="8865" yWindow="1125" windowWidth="25020" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Alternate functions" sheetId="4" r:id="rId1"/>
@@ -1891,7 +1891,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1901,6 +1901,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1917,7 +1929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1926,6 +1938,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2474,7 +2492,7 @@
       <c r="J2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>126</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -2533,7 +2551,7 @@
       <c r="J3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>119</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -3527,7 +3545,7 @@
       <c r="G20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="5" t="s">
         <v>166</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -3586,7 +3604,7 @@
       <c r="G21" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="5" t="s">
         <v>107</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -3645,7 +3663,7 @@
       <c r="G22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="5" t="s">
         <v>194</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -3704,7 +3722,7 @@
       <c r="G23" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="5" t="s">
         <v>192</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -4943,7 +4961,7 @@
       <c r="G44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="5" t="s">
         <v>182</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -7543,7 +7561,7 @@
       <c r="G90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="5" t="s">
         <v>182</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -9251,7 +9269,7 @@
       <c r="K122" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L122" s="1" t="s">
+      <c r="L122" s="4" t="s">
         <v>343</v>
       </c>
       <c r="M122" s="1" t="s">
@@ -9304,7 +9322,7 @@
       <c r="K123" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L123" s="1" t="s">
+      <c r="L123" s="4" t="s">
         <v>346</v>
       </c>
       <c r="M123" s="1" t="s">

--- a/Documents/uno_q_pin_info.xlsx
+++ b/Documents/uno_q_pin_info.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_UNO_Q\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044E281D-BB9A-46B6-B865-6BB9B19C1396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811797C3-C53B-47BE-8BFB-88439DECF1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8865" yWindow="1125" windowWidth="25020" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
+    <workbookView xWindow="3405" yWindow="1125" windowWidth="30480" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Alternate functions" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'Alternate functions'!$C$1:$S$138</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'Alternate functions'!$C$1:$T$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="583">
   <si>
     <t>PE2</t>
   </si>
@@ -1863,6 +1863,18 @@
   </si>
   <si>
     <t>D13</t>
+  </si>
+  <si>
+    <t>Tolerant</t>
+  </si>
+  <si>
+    <t>5v</t>
+  </si>
+  <si>
+    <t>3,6v</t>
+  </si>
+  <si>
+    <t>3,6</t>
   </si>
 </sst>
 </file>
@@ -1891,7 +1903,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1916,6 +1928,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1929,7 +1947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1946,11 +1964,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2028,31 +2052,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}" name="Table1" displayName="Table1" ref="A1:S138" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:S138" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}" name="Table1" displayName="Table1" ref="A1:T138" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:T138" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T138">
     <sortCondition ref="A1:A138"/>
   </sortState>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{5D3DC2F8-BE01-4770-90D9-5E86DD3515C5}" name="Arduino Pin" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4DF36108-303C-4552-A60D-FC0595910492}" name="usage" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{5811D300-4E1E-42C2-907B-C9CB2B8C6F0D}" name="Port" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="0"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{5D3DC2F8-BE01-4770-90D9-5E86DD3515C5}" name="Arduino Pin" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{4DF36108-303C-4552-A60D-FC0595910492}" name="usage" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{5811D300-4E1E-42C2-907B-C9CB2B8C6F0D}" name="Port" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{A25879C6-B528-4988-8519-F72B117DA08E}" name="Tolerant" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2378,31 +2403,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:T138"/>
   <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.5703125" style="1"/>
-    <col min="3" max="3" width="11.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="16.5703125" style="1"/>
+    <col min="3" max="4" width="11.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="16.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>541</v>
       </c>
@@ -2413,55 +2438,58 @@
         <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2472,55 +2500,58 @@
         <v>179</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2531,55 +2562,58 @@
         <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2590,55 +2624,58 @@
         <v>158</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2648,56 +2685,59 @@
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
+      <c r="D5" s="6" t="s">
+        <v>582</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2708,38 +2748,38 @@
         <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2753,10 +2793,13 @@
         <v>1</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2767,38 +2810,38 @@
         <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O7" s="1" t="s">
         <v>1</v>
       </c>
@@ -2812,10 +2855,13 @@
         <v>1</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2826,55 +2872,58 @@
         <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="S8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2885,29 +2934,29 @@
         <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L9" s="1" t="s">
         <v>1</v>
       </c>
@@ -2915,14 +2964,14 @@
         <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q9" s="1" t="s">
         <v>1</v>
       </c>
@@ -2930,10 +2979,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2944,55 +2996,58 @@
         <v>163</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3003,55 +3058,58 @@
         <v>184</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="S11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3062,55 +3120,58 @@
         <v>187</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3121,29 +3182,29 @@
         <v>206</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L13" s="1" t="s">
         <v>1</v>
       </c>
@@ -3154,22 +3215,25 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3180,55 +3244,58 @@
         <v>202</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="S14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3239,38 +3306,38 @@
         <v>199</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O15" s="1" t="s">
         <v>1</v>
       </c>
@@ -3278,16 +3345,19 @@
         <v>1</v>
       </c>
       <c r="Q15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="S15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3297,8 +3367,8 @@
       <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>1</v>
+      <c r="D16" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>1</v>
@@ -3307,46 +3377,49 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="S16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3356,33 +3429,33 @@
       <c r="C17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M17" s="1" t="s">
         <v>1</v>
       </c>
@@ -3399,13 +3472,16 @@
         <v>1</v>
       </c>
       <c r="R17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="S17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3416,55 +3492,58 @@
         <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="S18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3475,55 +3554,58 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3534,55 +3616,58 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3593,35 +3678,35 @@
         <v>19</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N21" s="1" t="s">
         <v>1</v>
       </c>
@@ -3629,19 +3714,22 @@
         <v>1</v>
       </c>
       <c r="P21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="S21" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3652,55 +3740,58 @@
         <v>193</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="Q22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3711,55 +3802,58 @@
         <v>191</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S23" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3770,29 +3864,29 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G24" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L24" s="1" t="s">
         <v>1</v>
       </c>
@@ -3800,14 +3894,14 @@
         <v>1</v>
       </c>
       <c r="N24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q24" s="1" t="s">
         <v>1</v>
       </c>
@@ -3815,10 +3909,13 @@
         <v>1</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3829,26 +3926,26 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K25" s="1" t="s">
         <v>1</v>
       </c>
@@ -3859,25 +3956,28 @@
         <v>1</v>
       </c>
       <c r="N25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3888,7 +3988,7 @@
         <v>240</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>1</v>
@@ -3902,12 +4002,12 @@
       <c r="H26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K26" s="1" t="s">
         <v>1</v>
       </c>
@@ -3915,28 +4015,31 @@
         <v>1</v>
       </c>
       <c r="M26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="Q26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3947,55 +4050,58 @@
         <v>218</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4006,17 +4112,17 @@
         <v>241</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H28" s="1" t="s">
         <v>1</v>
       </c>
@@ -4027,34 +4133,37 @@
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="R28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S28" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4065,55 +4174,58 @@
         <v>221</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="P29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="S29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4124,20 +4236,20 @@
         <v>0</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I30" s="1" t="s">
         <v>1</v>
       </c>
@@ -4151,28 +4263,31 @@
         <v>1</v>
       </c>
       <c r="M30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4183,20 +4298,20 @@
         <v>224</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I31" s="1" t="s">
         <v>1</v>
       </c>
@@ -4210,28 +4325,31 @@
         <v>1</v>
       </c>
       <c r="M31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="Q31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="S31" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4242,20 +4360,20 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I32" s="1" t="s">
         <v>1</v>
       </c>
@@ -4269,28 +4387,31 @@
         <v>1</v>
       </c>
       <c r="M32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="R32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S32" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4301,23 +4422,23 @@
         <v>226</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J33" s="1" t="s">
         <v>1</v>
       </c>
@@ -4328,28 +4449,31 @@
         <v>1</v>
       </c>
       <c r="M33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S33" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="S33" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4360,55 +4484,58 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="Q34" s="1" t="s">
+      <c r="R34" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4419,55 +4546,58 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="R35" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="R35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S35" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4478,20 +4608,20 @@
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I36" s="1" t="s">
         <v>1</v>
       </c>
@@ -4508,25 +4638,28 @@
         <v>1</v>
       </c>
       <c r="N36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="R36" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="R36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S36" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4537,7 +4670,7 @@
         <v>318</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>1</v>
@@ -4546,17 +4679,17 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K37" s="1" t="s">
         <v>1</v>
       </c>
@@ -4567,11 +4700,11 @@
         <v>1</v>
       </c>
       <c r="N37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P37" s="1" t="s">
         <v>1</v>
       </c>
@@ -4582,10 +4715,13 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4596,14 +4732,14 @@
         <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G38" s="1" t="s">
         <v>1</v>
       </c>
@@ -4614,11 +4750,11 @@
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L38" s="1" t="s">
         <v>1</v>
       </c>
@@ -4632,19 +4768,22 @@
         <v>1</v>
       </c>
       <c r="P38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="R38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S38" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4655,7 +4794,7 @@
         <v>320</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>1</v>
@@ -4664,17 +4803,17 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K39" s="1" t="s">
         <v>1</v>
       </c>
@@ -4685,11 +4824,11 @@
         <v>1</v>
       </c>
       <c r="N39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P39" s="1" t="s">
         <v>1</v>
       </c>
@@ -4700,10 +4839,13 @@
         <v>1</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4714,14 +4856,14 @@
         <v>44</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G40" s="1" t="s">
         <v>1</v>
       </c>
@@ -4732,11 +4874,11 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L40" s="1" t="s">
         <v>1</v>
       </c>
@@ -4750,19 +4892,22 @@
         <v>1</v>
       </c>
       <c r="P40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="Q40" s="1" t="s">
+      <c r="R40" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="R40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S40" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4773,7 +4918,7 @@
         <v>321</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>1</v>
@@ -4782,17 +4927,17 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K41" s="1" t="s">
         <v>1</v>
       </c>
@@ -4803,11 +4948,11 @@
         <v>1</v>
       </c>
       <c r="N41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P41" s="1" t="s">
         <v>1</v>
       </c>
@@ -4818,10 +4963,13 @@
         <v>1</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4832,7 +4980,7 @@
         <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>1</v>
@@ -4844,11 +4992,11 @@
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J42" s="1" t="s">
         <v>1</v>
       </c>
@@ -4859,28 +5007,31 @@
         <v>1</v>
       </c>
       <c r="M42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="N42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="Q42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4891,17 +5042,17 @@
         <v>252</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H43" s="1" t="s">
         <v>1</v>
       </c>
@@ -4912,34 +5063,37 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="R43" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="S43" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4950,7 +5104,7 @@
         <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>1</v>
@@ -4961,12 +5115,12 @@
       <c r="G44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J44" s="1" t="s">
         <v>1</v>
       </c>
@@ -4977,28 +5131,31 @@
         <v>1</v>
       </c>
       <c r="M44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="N44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="Q44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5009,7 +5166,7 @@
         <v>319</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>1</v>
@@ -5018,17 +5175,17 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K45" s="1" t="s">
         <v>1</v>
       </c>
@@ -5039,11 +5196,11 @@
         <v>1</v>
       </c>
       <c r="N45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P45" s="1" t="s">
         <v>1</v>
       </c>
@@ -5054,10 +5211,13 @@
         <v>1</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5067,21 +5227,21 @@
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>1</v>
+      <c r="D46" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I46" s="1" t="s">
         <v>1</v>
       </c>
@@ -5089,34 +5249,37 @@
         <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="M46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="O46" s="1" t="s">
+      <c r="P46" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R46" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="R46" s="1" t="s">
+      <c r="S46" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="S46" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T46" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5127,7 +5290,7 @@
         <v>251</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>1</v>
@@ -5148,34 +5311,37 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="Q47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5186,55 +5352,58 @@
         <v>23</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="M48" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="M48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="Q48" s="1" t="s">
+      <c r="R48" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="R48" s="1" t="s">
+      <c r="S48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="S48" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5245,55 +5414,58 @@
         <v>110</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M49" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="O49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="Q49" s="1" t="s">
+      <c r="R49" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="R49" s="1" t="s">
+      <c r="S49" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="S49" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T49" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5304,55 +5476,58 @@
         <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L50" s="1" t="s">
+      <c r="M50" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="M50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="O50" s="1" t="s">
+      <c r="P50" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S50" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="S50" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T50" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5363,55 +5538,58 @@
         <v>120</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="O51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R51" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="R51" s="1" t="s">
+      <c r="S51" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="S51" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T51" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5422,26 +5600,26 @@
         <v>305</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K52" s="1" t="s">
         <v>1</v>
       </c>
@@ -5452,11 +5630,11 @@
         <v>1</v>
       </c>
       <c r="N52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P52" s="1" t="s">
         <v>1</v>
       </c>
@@ -5467,10 +5645,13 @@
         <v>1</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5481,26 +5662,26 @@
         <v>306</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K53" s="1" t="s">
         <v>1</v>
       </c>
@@ -5511,11 +5692,11 @@
         <v>1</v>
       </c>
       <c r="N53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="O53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P53" s="1" t="s">
         <v>1</v>
       </c>
@@ -5526,10 +5707,13 @@
         <v>1</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -5540,26 +5724,26 @@
         <v>307</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K54" s="1" t="s">
         <v>1</v>
       </c>
@@ -5570,11 +5754,11 @@
         <v>1</v>
       </c>
       <c r="N54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="O54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P54" s="1" t="s">
         <v>1</v>
       </c>
@@ -5585,10 +5769,13 @@
         <v>1</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -5599,7 +5786,7 @@
         <v>308</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>1</v>
@@ -5608,11 +5795,11 @@
         <v>1</v>
       </c>
       <c r="G55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I55" s="1" t="s">
         <v>1</v>
       </c>
@@ -5626,11 +5813,11 @@
         <v>1</v>
       </c>
       <c r="M55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="N55" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O55" s="1" t="s">
         <v>1</v>
       </c>
@@ -5644,10 +5831,13 @@
         <v>1</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -5658,7 +5848,7 @@
         <v>309</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>1</v>
@@ -5667,11 +5857,11 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5685,14 +5875,14 @@
         <v>1</v>
       </c>
       <c r="M56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N56" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="O56" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="O56" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5703,10 +5893,13 @@
         <v>1</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -5717,7 +5910,7 @@
         <v>310</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>1</v>
@@ -5726,17 +5919,17 @@
         <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K57" s="1" t="s">
         <v>1</v>
       </c>
@@ -5747,11 +5940,11 @@
         <v>1</v>
       </c>
       <c r="N57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="O57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P57" s="1" t="s">
         <v>1</v>
       </c>
@@ -5762,10 +5955,13 @@
         <v>1</v>
       </c>
       <c r="S57" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -5776,7 +5972,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>1</v>
@@ -5788,14 +5984,14 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K58" s="1" t="s">
         <v>1</v>
       </c>
@@ -5812,19 +6008,22 @@
         <v>1</v>
       </c>
       <c r="P58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="Q58" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S58" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -5835,7 +6034,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>1</v>
@@ -5847,14 +6046,14 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K59" s="1" t="s">
         <v>1</v>
       </c>
@@ -5871,19 +6070,22 @@
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="Q59" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -5894,26 +6096,26 @@
         <v>10</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K60" s="1" t="s">
         <v>1</v>
       </c>
@@ -5930,19 +6132,22 @@
         <v>1</v>
       </c>
       <c r="P60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="Q60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -5953,26 +6158,26 @@
         <v>11</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K61" s="1" t="s">
         <v>1</v>
       </c>
@@ -5989,19 +6194,22 @@
         <v>1</v>
       </c>
       <c r="P61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="Q61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6012,26 +6220,26 @@
         <v>12</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K62" s="1" t="s">
         <v>1</v>
       </c>
@@ -6048,19 +6256,22 @@
         <v>1</v>
       </c>
       <c r="P62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="Q62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6071,26 +6282,26 @@
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K63" s="1" t="s">
         <v>1</v>
       </c>
@@ -6107,19 +6318,22 @@
         <v>1</v>
       </c>
       <c r="P63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="Q63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6130,26 +6344,26 @@
         <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K64" s="1" t="s">
         <v>1</v>
       </c>
@@ -6160,25 +6374,28 @@
         <v>1</v>
       </c>
       <c r="N64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R64" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="R64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S64" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6189,17 +6406,17 @@
         <v>15</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H65" s="1" t="s">
         <v>1</v>
       </c>
@@ -6216,28 +6433,31 @@
         <v>1</v>
       </c>
       <c r="M65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R65" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S65" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6248,23 +6468,23 @@
         <v>16</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J66" s="1" t="s">
         <v>1</v>
       </c>
@@ -6275,28 +6495,31 @@
         <v>1</v>
       </c>
       <c r="M66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="N66" s="1" t="s">
+      <c r="O66" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R66" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="R66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S66" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6307,23 +6530,23 @@
         <v>17</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J67" s="1" t="s">
         <v>1</v>
       </c>
@@ -6337,25 +6560,28 @@
         <v>1</v>
       </c>
       <c r="N67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="O67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P67" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R67" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R67" s="1" t="s">
+      <c r="S67" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="S67" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T67" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6366,7 +6592,7 @@
         <v>18</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>1</v>
@@ -6375,20 +6601,20 @@
         <v>1</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L68" s="1" t="s">
         <v>1</v>
       </c>
@@ -6396,25 +6622,28 @@
         <v>1</v>
       </c>
       <c r="N68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="O68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P68" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R68" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="R68" s="1" t="s">
+      <c r="S68" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="S68" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T68" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6425,7 +6654,7 @@
         <v>291</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>1</v>
@@ -6437,20 +6666,20 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M69" s="1" t="s">
         <v>1</v>
       </c>
@@ -6461,19 +6690,22 @@
         <v>1</v>
       </c>
       <c r="P69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="Q69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R69" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6484,55 +6716,58 @@
         <v>25</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="O70" s="1" t="s">
+      <c r="P70" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="P70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S70" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="S70" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T70" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6543,7 +6778,7 @@
         <v>298</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>1</v>
@@ -6588,22 +6823,25 @@
         <v>1</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G72" s="1" t="s">
         <v>1</v>
       </c>
@@ -6626,49 +6864,52 @@
         <v>1</v>
       </c>
       <c r="N72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P72" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R72" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="R72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S72" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G73" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K73" s="1" t="s">
         <v>1</v>
       </c>
@@ -6679,58 +6920,61 @@
         <v>1</v>
       </c>
       <c r="N73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P73" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R73" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S73" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N74" s="1" t="s">
         <v>1</v>
       </c>
@@ -6741,46 +6985,49 @@
         <v>1</v>
       </c>
       <c r="Q74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R74" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="R74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S74" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M75" s="1" t="s">
         <v>1</v>
       </c>
@@ -6794,237 +7041,252 @@
         <v>1</v>
       </c>
       <c r="Q75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R75" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="R75" s="1" t="s">
+      <c r="S75" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T75" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="J76" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="N76" s="1" t="s">
+      <c r="O76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R76" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="R76" s="1" t="s">
+      <c r="S76" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="S76" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T76" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="N77" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="O77" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="Q77" s="1" t="s">
+      <c r="R77" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="R77" s="1" t="s">
+      <c r="S77" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="S77" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T77" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="1" t="s">
         <v>229</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I78" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="O78" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="O78" s="1" t="s">
+      <c r="P78" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="P78" s="1" t="s">
+      <c r="Q78" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="Q78" s="1" t="s">
+      <c r="R78" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="R78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S78" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F79" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H79" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="N79" s="1" t="s">
+      <c r="O79" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="O79" s="1" t="s">
+      <c r="P79" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="P79" s="1" t="s">
+      <c r="Q79" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="Q79" s="1" t="s">
+      <c r="R79" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="R79" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S79" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T79" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>235</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F80" s="1" t="s">
         <v>1</v>
       </c>
@@ -7038,42 +7300,45 @@
         <v>1</v>
       </c>
       <c r="J80" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="M80" s="1" t="s">
+      <c r="N80" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="O80" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="O80" s="1" t="s">
+      <c r="P80" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="P80" s="1" t="s">
+      <c r="Q80" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="Q80" s="1" t="s">
+      <c r="R80" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="R80" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S80" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T80" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>1</v>
@@ -7118,15 +7383,18 @@
         <v>1</v>
       </c>
       <c r="S81" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>1</v>
@@ -7171,15 +7439,18 @@
         <v>1</v>
       </c>
       <c r="S82" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>1</v>
@@ -7224,15 +7495,18 @@
         <v>1</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>1</v>
@@ -7253,20 +7527,20 @@
         <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L84" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M84" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="O84" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P84" s="1" t="s">
         <v>1</v>
       </c>
@@ -7277,40 +7551,43 @@
         <v>1</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J85" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M85" s="1" t="s">
         <v>1</v>
       </c>
@@ -7330,15 +7607,18 @@
         <v>1</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>1</v>
@@ -7347,17 +7627,17 @@
         <v>1</v>
       </c>
       <c r="G86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K86" s="1" t="s">
         <v>1</v>
       </c>
@@ -7365,43 +7645,46 @@
         <v>1</v>
       </c>
       <c r="M86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N86" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O86" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="Q86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R86" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H87" s="1" t="s">
         <v>1</v>
       </c>
@@ -7412,39 +7695,42 @@
         <v>1</v>
       </c>
       <c r="K87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="L87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N87" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="N87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O87" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="Q87" s="1" t="s">
+      <c r="R87" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="R87" s="1" t="s">
+      <c r="S87" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="S87" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T87" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>1</v>
@@ -7456,117 +7742,123 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J88" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L88" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N88" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="N88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O88" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="Q88" s="1" t="s">
+      <c r="R88" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R88" s="1" t="s">
+      <c r="S88" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="S88" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T88" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I89" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N89" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="N89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="Q89" s="1" t="s">
+      <c r="R89" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="R89" s="1" t="s">
+      <c r="S89" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="S89" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T89" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>257</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="5" t="s">
+      <c r="H90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J90" s="1" t="s">
         <v>1</v>
       </c>
@@ -7577,43 +7869,46 @@
         <v>1</v>
       </c>
       <c r="M90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N90" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="N90" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P90" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="P90" s="1" t="s">
+      <c r="Q90" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Q90" s="1" t="s">
+      <c r="R90" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="R90" s="1" t="s">
+      <c r="S90" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="S90" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T90" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H91" s="1" t="s">
         <v>1</v>
       </c>
@@ -7639,34 +7934,37 @@
         <v>1</v>
       </c>
       <c r="P91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="Q91" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S91" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="S91" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T91" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H92" s="1" t="s">
         <v>1</v>
       </c>
@@ -7692,24 +7990,27 @@
         <v>1</v>
       </c>
       <c r="P92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="Q92" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S92" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="S92" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T92" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>1</v>
@@ -7718,51 +8019,54 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H93" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M93" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="O93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="Q93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R93" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>1</v>
@@ -7777,45 +8081,48 @@
         <v>1</v>
       </c>
       <c r="I94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O94" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="O94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="Q94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>1</v>
@@ -7830,45 +8137,48 @@
         <v>1</v>
       </c>
       <c r="I95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L95" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="O95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="Q95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S95" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>1</v>
@@ -7877,51 +8187,54 @@
         <v>1</v>
       </c>
       <c r="G96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="I96" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L96" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M96" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O96" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="O96" s="1" t="s">
+      <c r="P96" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="P96" s="1" t="s">
+      <c r="Q96" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="Q96" s="1" t="s">
+      <c r="R96" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="R96" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S96" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>1</v>
@@ -7939,52 +8252,55 @@
         <v>1</v>
       </c>
       <c r="J97" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K97" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="L97" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L97" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M97" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N97" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O97" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="O97" s="1" t="s">
+      <c r="P97" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="P97" s="1" t="s">
+      <c r="Q97" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="Q97" s="1" t="s">
+      <c r="R97" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="R97" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S97" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H98" s="1" t="s">
         <v>1</v>
       </c>
@@ -8004,30 +8320,33 @@
         <v>1</v>
       </c>
       <c r="N98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="O98" s="1" t="s">
+      <c r="P98" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="P98" s="1" t="s">
+      <c r="Q98" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="Q98" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S98" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="S98" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T98" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>1</v>
@@ -8057,90 +8376,96 @@
         <v>1</v>
       </c>
       <c r="N99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O99" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="O99" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="Q99" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S99" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="S99" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T99" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I100" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L100" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N100" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="N100" s="1" t="s">
+      <c r="O100" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="O100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="Q100" s="1" t="s">
+      <c r="R100" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S100" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G101" s="1" t="s">
         <v>1</v>
       </c>
@@ -8148,52 +8473,55 @@
         <v>1</v>
       </c>
       <c r="I101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J101" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L101" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N101" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="N101" s="1" t="s">
+      <c r="O101" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="O101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="Q101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R101" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G102" s="1" t="s">
         <v>1</v>
       </c>
@@ -8201,52 +8529,55 @@
         <v>1</v>
       </c>
       <c r="I102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L102" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N102" s="1" t="s">
+      <c r="O102" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="O102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="Q102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R102" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T102" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G103" s="1" t="s">
         <v>1</v>
       </c>
@@ -8254,64 +8585,67 @@
         <v>1</v>
       </c>
       <c r="I103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="K103" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N103" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="N103" s="1" t="s">
+      <c r="O103" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="O103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="Q103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H104" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K104" s="1" t="s">
         <v>1</v>
       </c>
@@ -8322,49 +8656,52 @@
         <v>1</v>
       </c>
       <c r="N104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O104" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="O104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="Q104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R104" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T104" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J105" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K105" s="1" t="s">
         <v>1</v>
       </c>
@@ -8375,52 +8712,55 @@
         <v>1</v>
       </c>
       <c r="N105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O105" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="O105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="Q105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R105" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I106" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L106" s="1" t="s">
         <v>1</v>
       </c>
@@ -8428,30 +8768,33 @@
         <v>1</v>
       </c>
       <c r="N106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O106" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="O106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="Q106" s="1" t="s">
+      <c r="R106" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="R106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S106" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>1</v>
@@ -8460,11 +8803,11 @@
         <v>1</v>
       </c>
       <c r="G107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I107" s="1" t="s">
         <v>1</v>
       </c>
@@ -8481,30 +8824,33 @@
         <v>1</v>
       </c>
       <c r="N107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O107" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="O107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P107" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R107" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="R107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S107" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>1</v>
@@ -8519,11 +8865,11 @@
         <v>1</v>
       </c>
       <c r="I108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J108" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K108" s="1" t="s">
         <v>1</v>
       </c>
@@ -8540,24 +8886,27 @@
         <v>1</v>
       </c>
       <c r="P108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="Q108" s="1" t="s">
+      <c r="R108" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="R108" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S108" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C109" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>1</v>
@@ -8569,11 +8918,11 @@
         <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J109" s="1" t="s">
         <v>1</v>
       </c>
@@ -8590,27 +8939,30 @@
         <v>1</v>
       </c>
       <c r="O109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P109" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="P109" s="1" t="s">
+      <c r="Q109" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="Q109" s="1" t="s">
+      <c r="R109" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="R109" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S109" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>1</v>
@@ -8625,11 +8977,11 @@
         <v>1</v>
       </c>
       <c r="I110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K110" s="1" t="s">
         <v>1</v>
       </c>
@@ -8637,33 +8989,36 @@
         <v>1</v>
       </c>
       <c r="M110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N110" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="N110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O110" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="Q110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R110" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>1</v>
@@ -8678,11 +9033,11 @@
         <v>1</v>
       </c>
       <c r="I111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J111" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K111" s="1" t="s">
         <v>1</v>
       </c>
@@ -8690,40 +9045,43 @@
         <v>1</v>
       </c>
       <c r="M111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N111" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="N111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O111" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q111" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="Q111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R111" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T111" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C112" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G112" s="1" t="s">
         <v>1</v>
       </c>
@@ -8731,17 +9089,17 @@
         <v>1</v>
       </c>
       <c r="I112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J112" s="1" t="s">
+      <c r="K112" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K112" s="1" t="s">
+      <c r="L112" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L112" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M112" s="1" t="s">
         <v>1</v>
       </c>
@@ -8752,49 +9110,52 @@
         <v>1</v>
       </c>
       <c r="P112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="Q112" s="1" t="s">
+      <c r="R112" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="R112" s="1" t="s">
+      <c r="S112" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="S112" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T112" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="1" t="s">
         <v>288</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I113" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J113" s="2" t="s">
+      <c r="J113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="L113" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M113" s="1" t="s">
         <v>1</v>
       </c>
@@ -8808,28 +9169,31 @@
         <v>1</v>
       </c>
       <c r="Q113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R113" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="R113" s="1" t="s">
+      <c r="S113" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="S113" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T113" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G114" s="1" t="s">
         <v>1</v>
       </c>
@@ -8837,17 +9201,17 @@
         <v>1</v>
       </c>
       <c r="I114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J114" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J114" s="2" t="s">
+      <c r="K114" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K114" s="1" t="s">
+      <c r="L114" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M114" s="1" t="s">
         <v>1</v>
       </c>
@@ -8858,40 +9222,43 @@
         <v>1</v>
       </c>
       <c r="P114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="Q114" s="1" t="s">
+      <c r="R114" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S114" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="1" t="s">
         <v>292</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G115" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J115" s="1" t="s">
         <v>1</v>
       </c>
@@ -8911,43 +9278,46 @@
         <v>1</v>
       </c>
       <c r="P115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q115" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="Q115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R115" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="1" t="s">
         <v>293</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I116" s="1" t="s">
+      <c r="J116" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K116" s="1" t="s">
         <v>1</v>
       </c>
@@ -8958,11 +9328,11 @@
         <v>1</v>
       </c>
       <c r="N116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O116" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="O116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P116" s="1" t="s">
         <v>1</v>
       </c>
@@ -8973,15 +9343,18 @@
         <v>1</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="1" t="s">
         <v>277</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>1</v>
@@ -8996,11 +9369,11 @@
         <v>1</v>
       </c>
       <c r="I117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K117" s="1" t="s">
         <v>1</v>
       </c>
@@ -9017,24 +9390,27 @@
         <v>1</v>
       </c>
       <c r="P117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q117" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="Q117" s="1" t="s">
+      <c r="R117" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="R117" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S117" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T117" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>1</v>
@@ -9049,11 +9425,11 @@
         <v>1</v>
       </c>
       <c r="I118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J118" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K118" s="1" t="s">
         <v>1</v>
       </c>
@@ -9070,24 +9446,27 @@
         <v>1</v>
       </c>
       <c r="P118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="Q118" s="1" t="s">
+      <c r="R118" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="R118" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S118" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T118" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>1</v>
@@ -9102,11 +9481,11 @@
         <v>1</v>
       </c>
       <c r="I119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J119" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K119" s="1" t="s">
         <v>1</v>
       </c>
@@ -9123,24 +9502,27 @@
         <v>1</v>
       </c>
       <c r="P119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q119" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="Q119" s="1" t="s">
+      <c r="R119" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="R119" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S119" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>1</v>
@@ -9155,20 +9537,20 @@
         <v>1</v>
       </c>
       <c r="I120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K120" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M120" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="M120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N120" s="1" t="s">
         <v>1</v>
       </c>
@@ -9176,24 +9558,27 @@
         <v>1</v>
       </c>
       <c r="P120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="Q120" s="1" t="s">
+      <c r="R120" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="R120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S120" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>1</v>
@@ -9202,35 +9587,35 @@
         <v>1</v>
       </c>
       <c r="G121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="I121" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="J121" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M121" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P121" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="P121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q121" s="1" t="s">
         <v>1</v>
       </c>
@@ -9238,15 +9623,18 @@
         <v>1</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>1</v>
@@ -9255,51 +9643,54 @@
         <v>1</v>
       </c>
       <c r="G122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H122" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="I122" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="J122" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="K122" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K122" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L122" s="4" t="s">
+      <c r="L122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M122" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="M122" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N122" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P122" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="P122" s="1" t="s">
+      <c r="Q122" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="Q122" s="1" t="s">
+      <c r="R122" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="R122" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S122" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="1" t="s">
         <v>283</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>1</v>
@@ -9311,23 +9702,23 @@
         <v>1</v>
       </c>
       <c r="H123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I123" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J123" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K123" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L123" s="4" t="s">
+      <c r="L123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M123" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="M123" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N123" s="1" t="s">
         <v>1</v>
       </c>
@@ -9344,15 +9735,18 @@
         <v>1</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>1</v>
@@ -9367,17 +9761,17 @@
         <v>1</v>
       </c>
       <c r="I124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J124" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J124" s="2" t="s">
+      <c r="K124" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="L124" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M124" s="1" t="s">
         <v>1</v>
       </c>
@@ -9388,24 +9782,27 @@
         <v>1</v>
       </c>
       <c r="P124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="Q124" s="1" t="s">
+      <c r="R124" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="R124" s="1" t="s">
+      <c r="S124" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="S124" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T124" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="1" t="s">
         <v>294</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>1</v>
@@ -9450,15 +9847,18 @@
         <v>1</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="1" t="s">
         <v>295</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>1</v>
@@ -9503,15 +9903,18 @@
         <v>1</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T126" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>1</v>
@@ -9520,11 +9923,11 @@
         <v>1</v>
       </c>
       <c r="G127" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H127" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H127" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I127" s="1" t="s">
         <v>1</v>
       </c>
@@ -9556,15 +9959,18 @@
         <v>1</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T127" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="1" t="s">
         <v>299</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>1</v>
@@ -9576,14 +9982,14 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I128" s="1" t="s">
+      <c r="J128" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J128" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K128" s="1" t="s">
         <v>1</v>
       </c>
@@ -9594,11 +10000,11 @@
         <v>1</v>
       </c>
       <c r="N128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O128" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O128" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P128" s="1" t="s">
         <v>1</v>
       </c>
@@ -9609,15 +10015,18 @@
         <v>1</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T128" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="1" t="s">
         <v>300</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>1</v>
@@ -9629,11 +10038,11 @@
         <v>1</v>
       </c>
       <c r="H129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J129" s="1" t="s">
         <v>1</v>
       </c>
@@ -9647,11 +10056,11 @@
         <v>1</v>
       </c>
       <c r="N129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O129" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O129" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P129" s="1" t="s">
         <v>1</v>
       </c>
@@ -9662,15 +10071,18 @@
         <v>1</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T129" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="1" t="s">
         <v>301</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>1</v>
@@ -9682,14 +10094,14 @@
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I130" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I130" s="1" t="s">
+      <c r="J130" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J130" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K130" s="1" t="s">
         <v>1</v>
       </c>
@@ -9700,11 +10112,11 @@
         <v>1</v>
       </c>
       <c r="N130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O130" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="O130" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P130" s="1" t="s">
         <v>1</v>
       </c>
@@ -9715,15 +10127,18 @@
         <v>1</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T130" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="1" t="s">
         <v>302</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>1</v>
@@ -9735,14 +10150,14 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="J131" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J131" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K131" s="1" t="s">
         <v>1</v>
       </c>
@@ -9753,11 +10168,11 @@
         <v>1</v>
       </c>
       <c r="N131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O131" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="O131" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P131" s="1" t="s">
         <v>1</v>
       </c>
@@ -9768,15 +10183,18 @@
         <v>1</v>
       </c>
       <c r="S131" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T131" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="1" t="s">
         <v>303</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>1</v>
@@ -9788,14 +10206,14 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I132" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="J132" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J132" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K132" s="1" t="s">
         <v>1</v>
       </c>
@@ -9806,11 +10224,11 @@
         <v>1</v>
       </c>
       <c r="N132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O132" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="O132" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P132" s="1" t="s">
         <v>1</v>
       </c>
@@ -9821,15 +10239,18 @@
         <v>1</v>
       </c>
       <c r="S132" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T132" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>1</v>
@@ -9841,14 +10262,14 @@
         <v>1</v>
       </c>
       <c r="H133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I133" s="1" t="s">
+      <c r="J133" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K133" s="1" t="s">
         <v>1</v>
       </c>
@@ -9859,11 +10280,11 @@
         <v>1</v>
       </c>
       <c r="N133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O133" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="O133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P133" s="1" t="s">
         <v>1</v>
       </c>
@@ -9874,34 +10295,37 @@
         <v>1</v>
       </c>
       <c r="S133" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T133" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="1" t="s">
         <v>311</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G134" s="1" t="s">
+      <c r="H134" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J134" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K134" s="1" t="s">
         <v>1</v>
       </c>
@@ -9912,11 +10336,11 @@
         <v>1</v>
       </c>
       <c r="N134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O134" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="O134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P134" s="1" t="s">
         <v>1</v>
       </c>
@@ -9927,15 +10351,18 @@
         <v>1</v>
       </c>
       <c r="S134" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="135" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T134" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C135" s="1" t="s">
         <v>312</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>1</v>
@@ -9950,14 +10377,14 @@
         <v>1</v>
       </c>
       <c r="I135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J135" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J135" s="1" t="s">
+      <c r="K135" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="K135" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L135" s="1" t="s">
         <v>1</v>
       </c>
@@ -9965,11 +10392,11 @@
         <v>1</v>
       </c>
       <c r="N135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O135" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="O135" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P135" s="1" t="s">
         <v>1</v>
       </c>
@@ -9980,15 +10407,18 @@
         <v>1</v>
       </c>
       <c r="S135" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T135" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="1" t="s">
         <v>314</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>1</v>
@@ -9997,20 +10427,20 @@
         <v>1</v>
       </c>
       <c r="G136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J136" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J136" s="1" t="s">
+      <c r="K136" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L136" s="1" t="s">
         <v>1</v>
       </c>
@@ -10018,11 +10448,11 @@
         <v>1</v>
       </c>
       <c r="N136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O136" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="O136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P136" s="1" t="s">
         <v>1</v>
       </c>
@@ -10033,15 +10463,18 @@
         <v>1</v>
       </c>
       <c r="S136" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T136" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="1" t="s">
         <v>316</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>1</v>
@@ -10050,20 +10483,20 @@
         <v>1</v>
       </c>
       <c r="G137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J137" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J137" s="1" t="s">
+      <c r="K137" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="K137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L137" s="1" t="s">
         <v>1</v>
       </c>
@@ -10071,11 +10504,11 @@
         <v>1</v>
       </c>
       <c r="N137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O137" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="O137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P137" s="1" t="s">
         <v>1</v>
       </c>
@@ -10086,56 +10519,59 @@
         <v>1</v>
       </c>
       <c r="S137" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="138" spans="3:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D138" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T137" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E138" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="G138" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G138" s="1" t="s">
+      <c r="H138" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="J138" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J138" s="1" t="s">
+      <c r="K138" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="L138" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L138" s="1" t="s">
+      <c r="M138" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="M138" s="1" t="s">
+      <c r="N138" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="N138" s="1" t="s">
+      <c r="O138" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="O138" s="1" t="s">
+      <c r="P138" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="P138" s="1" t="s">
+      <c r="Q138" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="Q138" s="1" t="s">
+      <c r="R138" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="R138" s="1" t="s">
+      <c r="S138" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="S138" s="1" t="s">
+      <c r="T138" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Documents/uno_q_pin_info.xlsx
+++ b/Documents/uno_q_pin_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_UNO_Q\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811797C3-C53B-47BE-8BFB-88439DECF1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9067DA-1EAA-4203-A4C0-D5EB1065A6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1125" windowWidth="30480" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
+    <workbookView xWindow="-30" yWindow="1335" windowWidth="24690" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Alternate functions" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="607">
   <si>
     <t>PE2</t>
   </si>
@@ -1829,9 +1829,6 @@
     <t>D24/JSPI</t>
   </si>
   <si>
-    <t>JMISC</t>
-  </si>
-  <si>
     <t>LED3_R</t>
   </si>
   <si>
@@ -1875,6 +1872,81 @@
   </si>
   <si>
     <t>3,6</t>
+  </si>
+  <si>
+    <t>JMISC_1</t>
+  </si>
+  <si>
+    <t>JMISC_2</t>
+  </si>
+  <si>
+    <t>JMISC_3</t>
+  </si>
+  <si>
+    <t>JMISC_4</t>
+  </si>
+  <si>
+    <t>JMISC_5</t>
+  </si>
+  <si>
+    <t>JMISC_6</t>
+  </si>
+  <si>
+    <t>JMISC_7</t>
+  </si>
+  <si>
+    <t>JMISC_8</t>
+  </si>
+  <si>
+    <t>JMISC_9</t>
+  </si>
+  <si>
+    <t>JMISC_10</t>
+  </si>
+  <si>
+    <t>JMISC_11</t>
+  </si>
+  <si>
+    <t>JMISC_12</t>
+  </si>
+  <si>
+    <t>JMISC_13</t>
+  </si>
+  <si>
+    <t>JMISC_14</t>
+  </si>
+  <si>
+    <t>JMISC_15</t>
+  </si>
+  <si>
+    <t>JMISC_16</t>
+  </si>
+  <si>
+    <t>JMISC_17</t>
+  </si>
+  <si>
+    <t>JMISC_18</t>
+  </si>
+  <si>
+    <t>JMISC_19</t>
+  </si>
+  <si>
+    <t>JMISC_20</t>
+  </si>
+  <si>
+    <t>JMISC_21</t>
+  </si>
+  <si>
+    <t>JMISC_22</t>
+  </si>
+  <si>
+    <t>JMISC_23</t>
+  </si>
+  <si>
+    <t>JMISC_24</t>
+  </si>
+  <si>
+    <t>JMISC_25</t>
   </si>
 </sst>
 </file>
@@ -2061,23 +2133,23 @@
     <tableColumn id="1" xr3:uid="{5D3DC2F8-BE01-4770-90D9-5E86DD3515C5}" name="Arduino Pin" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{4DF36108-303C-4552-A60D-FC0595910492}" name="usage" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{5811D300-4E1E-42C2-907B-C9CB2B8C6F0D}" name="Port" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{A25879C6-B528-4988-8519-F72B117DA08E}" name="Tolerant" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{A25879C6-B528-4988-8519-F72B117DA08E}" name="Tolerant" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2438,7 +2510,7 @@
         <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>53</v>
@@ -2500,7 +2572,7 @@
         <v>179</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>1</v>
@@ -2562,7 +2634,7 @@
         <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1</v>
@@ -2624,7 +2696,7 @@
         <v>158</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>159</v>
@@ -2686,7 +2758,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>1</v>
@@ -2748,7 +2820,7 @@
         <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>1</v>
@@ -2810,7 +2882,7 @@
         <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>1</v>
@@ -2872,7 +2944,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>1</v>
@@ -2934,7 +3006,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>1</v>
@@ -2996,7 +3068,7 @@
         <v>163</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>164</v>
@@ -3058,7 +3130,7 @@
         <v>184</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>1</v>
@@ -3120,7 +3192,7 @@
         <v>187</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>1</v>
@@ -3182,7 +3254,7 @@
         <v>206</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>207</v>
@@ -3244,7 +3316,7 @@
         <v>202</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>1</v>
@@ -3300,13 +3372,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>1</v>
@@ -3368,7 +3440,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>1</v>
@@ -3430,7 +3502,7 @@
         <v>28</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>92</v>
@@ -3492,7 +3564,7 @@
         <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>97</v>
@@ -3554,7 +3626,7 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>104</v>
@@ -3616,7 +3688,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>212</v>
@@ -3678,7 +3750,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>1</v>
@@ -3740,7 +3812,7 @@
         <v>193</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>1</v>
@@ -3802,7 +3874,7 @@
         <v>191</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>1</v>
@@ -3864,7 +3936,7 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>1</v>
@@ -3926,7 +3998,7 @@
         <v>22</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>1</v>
@@ -3988,7 +4060,7 @@
         <v>240</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>1</v>
@@ -4044,13 +4116,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>92</v>
@@ -4106,13 +4178,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>242</v>
@@ -4168,13 +4240,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>221</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>97</v>
@@ -4230,13 +4302,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>263</v>
@@ -4292,13 +4364,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>224</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>104</v>
@@ -4354,13 +4426,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>212</v>
@@ -4416,13 +4488,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>212</v>
@@ -4478,13 +4550,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>242</v>
@@ -4540,13 +4612,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>230</v>
@@ -4602,13 +4674,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>236</v>
@@ -4664,13 +4736,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>318</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>1</v>
@@ -4726,13 +4798,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>1</v>
@@ -4788,13 +4860,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>320</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>1</v>
@@ -4850,13 +4922,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>1</v>
@@ -4912,13 +4984,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>321</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>1</v>
@@ -4974,13 +5046,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>1</v>
@@ -5036,13 +5108,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>1</v>
@@ -5098,13 +5170,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>1</v>
@@ -5160,13 +5232,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>319</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>1</v>
@@ -5222,13 +5294,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>567</v>
+        <v>601</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>1</v>
@@ -5284,13 +5356,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>567</v>
+        <v>602</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>1</v>
@@ -5346,13 +5418,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>567</v>
+        <v>603</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>1</v>
@@ -5408,13 +5480,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>111</v>
@@ -5470,13 +5542,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>567</v>
+        <v>605</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>74</v>
@@ -5532,13 +5604,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>121</v>
@@ -5594,13 +5666,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>305</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>1</v>
@@ -5656,13 +5728,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>306</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>1</v>
@@ -5718,13 +5790,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>1</v>
@@ -5780,13 +5852,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>1</v>
@@ -5842,13 +5914,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>309</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>1</v>
@@ -5904,13 +5976,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>310</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>1</v>
@@ -5966,13 +6038,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>1</v>
@@ -6028,13 +6100,13 @@
         <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>1</v>
@@ -6090,13 +6162,13 @@
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>1</v>
@@ -6152,13 +6224,13 @@
         <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>1</v>
@@ -6214,13 +6286,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>1</v>
@@ -6276,13 +6348,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>1</v>
@@ -6338,13 +6410,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>1</v>
@@ -6400,13 +6472,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>1</v>
@@ -6462,13 +6534,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>1</v>
@@ -6524,13 +6596,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>1</v>
@@ -6586,13 +6658,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>1</v>
@@ -6648,13 +6720,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>291</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>1</v>
@@ -6710,13 +6782,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>1</v>
@@ -6772,13 +6844,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>298</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>1</v>
@@ -6834,7 +6906,7 @@
         <v>135</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>136</v>
@@ -6890,7 +6962,7 @@
         <v>138</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>139</v>
@@ -6946,7 +7018,7 @@
         <v>142</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>143</v>
@@ -7002,7 +7074,7 @@
         <v>115</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>1</v>
@@ -7058,7 +7130,7 @@
         <v>196</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>1</v>
@@ -7114,7 +7186,7 @@
         <v>168</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>1</v>
@@ -7170,7 +7242,7 @@
         <v>229</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>230</v>
@@ -7226,7 +7298,7 @@
         <v>232</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>1</v>
@@ -7282,7 +7354,7 @@
         <v>235</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>236</v>
@@ -7338,7 +7410,7 @@
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>1</v>
@@ -7394,7 +7466,7 @@
         <v>237</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>1</v>
@@ -7450,7 +7522,7 @@
         <v>238</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>1</v>
@@ -7506,7 +7578,7 @@
         <v>31</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>1</v>
@@ -7562,7 +7634,7 @@
         <v>32</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>1</v>
@@ -7618,7 +7690,7 @@
         <v>239</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>1</v>
@@ -7674,7 +7746,7 @@
         <v>253</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>1</v>
@@ -7730,7 +7802,7 @@
         <v>255</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>1</v>
@@ -7786,7 +7858,7 @@
         <v>256</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>1</v>
@@ -7842,7 +7914,7 @@
         <v>257</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>1</v>
@@ -7898,7 +7970,7 @@
         <v>258</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>1</v>
@@ -7954,7 +8026,7 @@
         <v>259</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>1</v>
@@ -8010,7 +8082,7 @@
         <v>244</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>1</v>
@@ -8066,7 +8138,7 @@
         <v>246</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>1</v>
@@ -8122,7 +8194,7 @@
         <v>247</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>1</v>
@@ -8178,7 +8250,7 @@
         <v>248</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>1</v>
@@ -8234,7 +8306,7 @@
         <v>250</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>1</v>
@@ -8290,7 +8362,7 @@
         <v>260</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>1</v>
@@ -8346,7 +8418,7 @@
         <v>262</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>1</v>
@@ -8402,7 +8474,7 @@
         <v>46</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>1</v>
@@ -8458,7 +8530,7 @@
         <v>47</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>1</v>
@@ -8514,7 +8586,7 @@
         <v>48</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>1</v>
@@ -8570,7 +8642,7 @@
         <v>49</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>1</v>
@@ -8626,7 +8698,7 @@
         <v>50</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>1</v>
@@ -8682,7 +8754,7 @@
         <v>51</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>1</v>
@@ -8738,7 +8810,7 @@
         <v>45</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>1</v>
@@ -8794,7 +8866,7 @@
         <v>36</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>1</v>
@@ -8850,7 +8922,7 @@
         <v>37</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>1</v>
@@ -8906,7 +8978,7 @@
         <v>38</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>1</v>
@@ -8962,7 +9034,7 @@
         <v>41</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>1</v>
@@ -9018,7 +9090,7 @@
         <v>42</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>1</v>
@@ -9074,7 +9146,7 @@
         <v>286</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>1</v>
@@ -9130,7 +9202,7 @@
         <v>288</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>1</v>
@@ -9186,7 +9258,7 @@
         <v>290</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>1</v>
@@ -9242,7 +9314,7 @@
         <v>292</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>1</v>
@@ -9298,7 +9370,7 @@
         <v>293</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>1</v>
@@ -9354,7 +9426,7 @@
         <v>277</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>1</v>
@@ -9410,7 +9482,7 @@
         <v>278</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>1</v>
@@ -9466,7 +9538,7 @@
         <v>279</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>1</v>
@@ -9522,7 +9594,7 @@
         <v>280</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>1</v>
@@ -9578,7 +9650,7 @@
         <v>281</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>1</v>
@@ -9634,7 +9706,7 @@
         <v>282</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>1</v>
@@ -9690,7 +9762,7 @@
         <v>283</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>1</v>
@@ -9746,7 +9818,7 @@
         <v>284</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>1</v>
@@ -9802,7 +9874,7 @@
         <v>294</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>1</v>
@@ -9858,7 +9930,7 @@
         <v>295</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>1</v>
@@ -9914,7 +9986,7 @@
         <v>296</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>1</v>
@@ -9970,7 +10042,7 @@
         <v>299</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>1</v>
@@ -10026,7 +10098,7 @@
         <v>300</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>1</v>
@@ -10082,7 +10154,7 @@
         <v>301</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>1</v>
@@ -10138,7 +10210,7 @@
         <v>302</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>1</v>
@@ -10194,7 +10266,7 @@
         <v>303</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>1</v>
@@ -10250,7 +10322,7 @@
         <v>304</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>1</v>
@@ -10306,7 +10378,7 @@
         <v>311</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>1</v>
@@ -10362,7 +10434,7 @@
         <v>312</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>1</v>
@@ -10418,7 +10490,7 @@
         <v>314</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>1</v>
@@ -10474,7 +10546,7 @@
         <v>316</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>1</v>

--- a/Documents/uno_q_pin_info.xlsx
+++ b/Documents/uno_q_pin_info.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Arduino_UNO_Q\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9067DA-1EAA-4203-A4C0-D5EB1065A6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DC2516-B41D-4D61-B965-7E2CD0E36251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="1335" windowWidth="24690" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
+    <workbookView xWindow="1515" yWindow="630" windowWidth="28110" windowHeight="19215" xr2:uid="{E4BC628E-A193-46B6-8015-32829E9A0B6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Alternate functions" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'Alternate functions'!$C$1:$T$138</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'Alternate functions'!$C$1:$U$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="632">
   <si>
     <t>PE2</t>
   </si>
@@ -1947,6 +1947,81 @@
   </si>
   <si>
     <t>JMISC_25</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>ADC14_1</t>
+  </si>
+  <si>
+    <t>ADC14_2</t>
+  </si>
+  <si>
+    <t>ADC14_3</t>
+  </si>
+  <si>
+    <t>ADC14_4</t>
+  </si>
+  <si>
+    <t>ADC1_5</t>
+  </si>
+  <si>
+    <t>ADC1_6</t>
+  </si>
+  <si>
+    <t>ADC1_7</t>
+  </si>
+  <si>
+    <t>ADC4_7</t>
+  </si>
+  <si>
+    <t>ADC1_8</t>
+  </si>
+  <si>
+    <t>ADC14_9</t>
+  </si>
+  <si>
+    <t>ADC14_10</t>
+  </si>
+  <si>
+    <t>ADC14_11</t>
+  </si>
+  <si>
+    <t>ADC1_12. 4_20</t>
+  </si>
+  <si>
+    <t>ADC1_13, 4_22</t>
+  </si>
+  <si>
+    <t>ADC1_14, 4_23</t>
+  </si>
+  <si>
+    <t>ADC1_15, 4_18</t>
+  </si>
+  <si>
+    <t>ADC1_16, 4_19</t>
+  </si>
+  <si>
+    <t>ADC1_17</t>
+  </si>
+  <si>
+    <t>ADC4_5</t>
+  </si>
+  <si>
+    <t>ADC4_6</t>
+  </si>
+  <si>
+    <t>ADC4_8</t>
+  </si>
+  <si>
+    <t>ADC4_15</t>
+  </si>
+  <si>
+    <t>ADC4_16</t>
+  </si>
+  <si>
+    <t>ADC4_17</t>
   </si>
 </sst>
 </file>
@@ -2019,7 +2094,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2039,11 +2114,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="23">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2124,32 +2205,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}" name="Table1" displayName="Table1" ref="A1:T138" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:T138" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}" name="Table1" displayName="Table1" ref="A1:U138" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:U138" xr:uid="{567E9095-4521-4CB8-B3C8-106A6ABBFE0F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U138">
     <sortCondition ref="A1:A138"/>
   </sortState>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{5D3DC2F8-BE01-4770-90D9-5E86DD3515C5}" name="Arduino Pin" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{4DF36108-303C-4552-A60D-FC0595910492}" name="usage" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{5811D300-4E1E-42C2-907B-C9CB2B8C6F0D}" name="Port" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{A25879C6-B528-4988-8519-F72B117DA08E}" name="Tolerant" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="0"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{5D3DC2F8-BE01-4770-90D9-5E86DD3515C5}" name="Arduino Pin" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{4DF36108-303C-4552-A60D-FC0595910492}" name="usage" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{5811D300-4E1E-42C2-907B-C9CB2B8C6F0D}" name="Port" dataDxfId="18"/>
+    <tableColumn id="20" xr3:uid="{A25879C6-B528-4988-8519-F72B117DA08E}" name="Tolerant" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{4E99670F-ADDD-4C52-9B09-5B2048858762}" name="ADC" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{74BE88FF-5CE3-461F-A123-4B7D553806F5}" name="AF0" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3954F4BC-2868-47FB-8E8F-45EC4574FF90}" name="AF1" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{1BD10078-5CBC-474B-9DA3-0ED9E02640CC}" name="AF2" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{BAF4C0D9-F5FC-4BD9-A3AD-6468389DB9A7}" name="AF3" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{5218359D-232A-41D1-B9D8-5007ACB972A9}" name="AF4" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{02FE55B4-3775-4437-94F3-8969261B600D}" name="AF5" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{9CB95CDE-98DB-4DC7-BC12-24E205076715}" name="AF6" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{E1BCDB17-8F81-4C96-8F69-5E6B75135343}" name="AF7" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{D3885D50-853B-47B8-9AB1-55C573D700A6}" name="AF8" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{8D8F5E86-F9E1-4B5B-A61E-708EC27FEA0C}" name="AF9" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{FB09A257-B323-4805-A01A-AE2A1C949B27}" name="AF10" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{6D47C5BB-E8B8-402F-B6DA-1A62C563C332}" name="AF11" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{A2BF269C-9E8F-4F38-899F-A0607D6FD01A}" name="AF12" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{60F5BB27-9C71-46A2-8A33-34B2F87EEFB2}" name="AF13" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{D03D8DB4-217F-4E09-8CE9-81318E9E3979}" name="AF14" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{D043E6A3-4209-4229-85F5-7672216074E8}" name="AF15" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2475,31 +2557,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T138"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.5703125" style="1"/>
-    <col min="3" max="4" width="11.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="16.5703125" style="1"/>
+    <col min="3" max="5" width="11.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="16.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>541</v>
       </c>
@@ -2513,55 +2595,58 @@
         <v>578</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2574,56 +2659,56 @@
       <c r="D2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2636,56 +2721,56 @@
       <c r="D3" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2698,56 +2783,56 @@
       <c r="D4" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="S4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2761,55 +2846,58 @@
         <v>581</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>623</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2822,39 +2910,36 @@
       <c r="D6" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P6" s="1" t="s">
         <v>1</v>
       </c>
@@ -2868,10 +2953,13 @@
         <v>1</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2884,39 +2972,36 @@
       <c r="D7" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
@@ -2930,10 +3015,13 @@
         <v>1</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2947,55 +3035,58 @@
         <v>579</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1</v>
+        <v>624</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3009,29 +3100,29 @@
         <v>579</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>625</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M9" s="1" t="s">
         <v>1</v>
       </c>
@@ -3039,14 +3130,14 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R9" s="1" t="s">
         <v>1</v>
       </c>
@@ -3054,10 +3145,13 @@
         <v>1</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3070,56 +3164,56 @@
       <c r="D10" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3132,56 +3226,56 @@
       <c r="D11" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -3194,56 +3288,56 @@
       <c r="D12" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -3256,30 +3350,27 @@
       <c r="D13" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M13" s="1" t="s">
         <v>1</v>
       </c>
@@ -3290,22 +3381,25 @@
         <v>1</v>
       </c>
       <c r="P13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -3318,56 +3412,56 @@
       <c r="D14" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -3380,39 +3474,36 @@
       <c r="D15" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P15" s="1" t="s">
         <v>1</v>
       </c>
@@ -3420,16 +3511,19 @@
         <v>1</v>
       </c>
       <c r="R15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -3443,7 +3537,7 @@
         <v>580</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1</v>
+        <v>617</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>1</v>
@@ -3452,46 +3546,49 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -3505,32 +3602,32 @@
         <v>580</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N17" s="1" t="s">
         <v>1</v>
       </c>
@@ -3547,13 +3644,16 @@
         <v>1</v>
       </c>
       <c r="S17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="T17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -3567,55 +3667,58 @@
         <v>579</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="Q18" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -3629,55 +3732,58 @@
         <v>579</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="T19" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="T19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -3691,55 +3797,58 @@
         <v>579</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="S20" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -3753,35 +3862,35 @@
         <v>579</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O21" s="1" t="s">
         <v>1</v>
       </c>
@@ -3789,19 +3898,22 @@
         <v>1</v>
       </c>
       <c r="Q21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="T21" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3814,56 +3926,56 @@
       <c r="D22" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="R22" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3876,56 +3988,56 @@
       <c r="D23" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T23" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3939,29 +4051,29 @@
         <v>579</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1</v>
+        <v>610</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H24" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M24" s="1" t="s">
         <v>1</v>
       </c>
@@ -3969,14 +4081,14 @@
         <v>1</v>
       </c>
       <c r="O24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="Q24" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R24" s="1" t="s">
         <v>1</v>
       </c>
@@ -3984,10 +4096,13 @@
         <v>1</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4001,26 +4116,26 @@
         <v>579</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>611</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L25" s="1" t="s">
         <v>1</v>
       </c>
@@ -4031,25 +4146,28 @@
         <v>1</v>
       </c>
       <c r="O25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="T25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4062,9 +4180,6 @@
       <c r="D26" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F26" s="1" t="s">
         <v>1</v>
       </c>
@@ -4077,12 +4192,12 @@
       <c r="I26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L26" s="1" t="s">
         <v>1</v>
       </c>
@@ -4090,28 +4205,31 @@
         <v>1</v>
       </c>
       <c r="N26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -4124,56 +4242,56 @@
       <c r="D27" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="S27" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T27" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4186,18 +4304,15 @@
       <c r="D28" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I28" s="1" t="s">
         <v>1</v>
       </c>
@@ -4208,34 +4323,37 @@
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="S28" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T28" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4248,56 +4366,56 @@
       <c r="D29" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="S29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="T29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4310,21 +4428,18 @@
       <c r="D30" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J30" s="1" t="s">
         <v>1</v>
       </c>
@@ -4338,28 +4453,31 @@
         <v>1</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T30" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4372,21 +4490,18 @@
       <c r="D31" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J31" s="1" t="s">
         <v>1</v>
       </c>
@@ -4400,28 +4515,31 @@
         <v>1</v>
       </c>
       <c r="N31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="R31" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T31" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4434,21 +4552,18 @@
       <c r="D32" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J32" s="1" t="s">
         <v>1</v>
       </c>
@@ -4462,28 +4577,31 @@
         <v>1</v>
       </c>
       <c r="N32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T32" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4496,24 +4614,21 @@
       <c r="D33" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K33" s="1" t="s">
         <v>1</v>
       </c>
@@ -4524,28 +4639,31 @@
         <v>1</v>
       </c>
       <c r="N33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="R33" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="T33" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4558,56 +4676,56 @@
       <c r="D34" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="R34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="S34" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4620,56 +4738,56 @@
       <c r="D35" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="P35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="R35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T35" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4682,21 +4800,18 @@
       <c r="D36" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J36" s="1" t="s">
         <v>1</v>
       </c>
@@ -4713,25 +4828,28 @@
         <v>1</v>
       </c>
       <c r="O36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="P36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="S36" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T36" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4744,9 +4862,6 @@
       <c r="D37" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F37" s="1" t="s">
         <v>1</v>
       </c>
@@ -4754,17 +4869,17 @@
         <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L37" s="1" t="s">
         <v>1</v>
       </c>
@@ -4775,11 +4890,11 @@
         <v>1</v>
       </c>
       <c r="O37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="P37" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q37" s="1" t="s">
         <v>1</v>
       </c>
@@ -4790,10 +4905,13 @@
         <v>1</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4806,15 +4924,12 @@
       <c r="D38" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H38" s="1" t="s">
         <v>1</v>
       </c>
@@ -4825,11 +4940,11 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M38" s="1" t="s">
         <v>1</v>
       </c>
@@ -4843,19 +4958,22 @@
         <v>1</v>
       </c>
       <c r="Q38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="S38" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T38" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4868,9 +4986,6 @@
       <c r="D39" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F39" s="1" t="s">
         <v>1</v>
       </c>
@@ -4878,17 +4993,17 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L39" s="1" t="s">
         <v>1</v>
       </c>
@@ -4899,11 +5014,11 @@
         <v>1</v>
       </c>
       <c r="O39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q39" s="1" t="s">
         <v>1</v>
       </c>
@@ -4914,10 +5029,13 @@
         <v>1</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4930,15 +5048,12 @@
       <c r="D40" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H40" s="1" t="s">
         <v>1</v>
       </c>
@@ -4949,11 +5064,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M40" s="1" t="s">
         <v>1</v>
       </c>
@@ -4967,19 +5082,22 @@
         <v>1</v>
       </c>
       <c r="Q40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="S40" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T40" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4992,9 +5110,6 @@
       <c r="D41" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F41" s="1" t="s">
         <v>1</v>
       </c>
@@ -5002,17 +5117,17 @@
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L41" s="1" t="s">
         <v>1</v>
       </c>
@@ -5023,11 +5138,11 @@
         <v>1</v>
       </c>
       <c r="O41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="P41" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q41" s="1" t="s">
         <v>1</v>
       </c>
@@ -5038,10 +5153,13 @@
         <v>1</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5055,7 +5173,7 @@
         <v>579</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1</v>
+        <v>626</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>1</v>
@@ -5067,11 +5185,11 @@
         <v>1</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K42" s="1" t="s">
         <v>1</v>
       </c>
@@ -5082,28 +5200,31 @@
         <v>1</v>
       </c>
       <c r="N42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="R42" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5116,18 +5237,15 @@
       <c r="D43" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I43" s="1" t="s">
         <v>1</v>
       </c>
@@ -5138,34 +5256,37 @@
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="T43" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5179,7 +5300,7 @@
         <v>579</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1</v>
+        <v>627</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>1</v>
@@ -5190,12 +5311,12 @@
       <c r="H44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K44" s="1" t="s">
         <v>1</v>
       </c>
@@ -5206,28 +5327,31 @@
         <v>1</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R44" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5240,9 +5364,6 @@
       <c r="D45" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F45" s="1" t="s">
         <v>1</v>
       </c>
@@ -5250,17 +5371,17 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L45" s="1" t="s">
         <v>1</v>
       </c>
@@ -5271,11 +5392,11 @@
         <v>1</v>
       </c>
       <c r="O45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P45" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q45" s="1" t="s">
         <v>1</v>
       </c>
@@ -5286,10 +5407,13 @@
         <v>1</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5303,20 +5427,20 @@
         <v>580</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1</v>
+        <v>616</v>
       </c>
       <c r="F46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J46" s="1" t="s">
         <v>1</v>
       </c>
@@ -5324,34 +5448,37 @@
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P46" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="P46" s="1" t="s">
+      <c r="Q46" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="Q46" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S46" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="S46" s="1" t="s">
+      <c r="T46" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="T46" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U46" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -5364,9 +5491,6 @@
       <c r="D47" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F47" s="1" t="s">
         <v>1</v>
       </c>
@@ -5386,34 +5510,37 @@
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="P47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R47" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="R47" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -5427,55 +5554,58 @@
         <v>579</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="M48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="N48" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="N48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P48" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R48" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="R48" s="1" t="s">
+      <c r="S48" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="S48" s="1" t="s">
+      <c r="T48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T48" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5488,56 +5618,56 @@
       <c r="D49" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N49" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R49" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="R49" s="1" t="s">
+      <c r="S49" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="S49" s="1" t="s">
+      <c r="T49" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="T49" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U49" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5551,55 +5681,58 @@
         <v>579</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="N50" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="N50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="P50" s="1" t="s">
+      <c r="Q50" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="Q50" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T50" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="T50" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U50" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5612,56 +5745,56 @@
       <c r="D51" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S51" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="S51" s="1" t="s">
+      <c r="T51" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="T51" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U51" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5674,27 +5807,24 @@
       <c r="D52" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L52" s="1" t="s">
         <v>1</v>
       </c>
@@ -5705,11 +5835,11 @@
         <v>1</v>
       </c>
       <c r="O52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q52" s="1" t="s">
         <v>1</v>
       </c>
@@ -5720,10 +5850,13 @@
         <v>1</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U52" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5736,27 +5869,24 @@
       <c r="D53" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L53" s="1" t="s">
         <v>1</v>
       </c>
@@ -5767,11 +5897,11 @@
         <v>1</v>
       </c>
       <c r="O53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q53" s="1" t="s">
         <v>1</v>
       </c>
@@ -5782,10 +5912,13 @@
         <v>1</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -5798,27 +5931,24 @@
       <c r="D54" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L54" s="1" t="s">
         <v>1</v>
       </c>
@@ -5829,11 +5959,11 @@
         <v>1</v>
       </c>
       <c r="O54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P54" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q54" s="1" t="s">
         <v>1</v>
       </c>
@@ -5844,10 +5974,13 @@
         <v>1</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -5860,9 +5993,6 @@
       <c r="D55" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F55" s="1" t="s">
         <v>1</v>
       </c>
@@ -5870,11 +6000,11 @@
         <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J55" s="1" t="s">
         <v>1</v>
       </c>
@@ -5888,11 +6018,11 @@
         <v>1</v>
       </c>
       <c r="N55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="O55" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P55" s="1" t="s">
         <v>1</v>
       </c>
@@ -5906,10 +6036,13 @@
         <v>1</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -5922,9 +6055,6 @@
       <c r="D56" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5932,11 +6062,11 @@
         <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5950,14 +6080,14 @@
         <v>1</v>
       </c>
       <c r="N56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O56" s="1" t="s">
+      <c r="P56" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q56" s="1" t="s">
         <v>1</v>
       </c>
@@ -5968,10 +6098,13 @@
         <v>1</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -5984,9 +6117,6 @@
       <c r="D57" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F57" s="1" t="s">
         <v>1</v>
       </c>
@@ -5994,17 +6124,17 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L57" s="1" t="s">
         <v>1</v>
       </c>
@@ -6015,11 +6145,11 @@
         <v>1</v>
       </c>
       <c r="O57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P57" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q57" s="1" t="s">
         <v>1</v>
       </c>
@@ -6030,10 +6160,13 @@
         <v>1</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -6046,9 +6179,6 @@
       <c r="D58" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F58" s="1" t="s">
         <v>1</v>
       </c>
@@ -6059,14 +6189,14 @@
         <v>1</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L58" s="1" t="s">
         <v>1</v>
       </c>
@@ -6083,19 +6213,22 @@
         <v>1</v>
       </c>
       <c r="Q58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R58" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="R58" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6108,9 +6241,6 @@
       <c r="D59" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F59" s="1" t="s">
         <v>1</v>
       </c>
@@ -6121,14 +6251,14 @@
         <v>1</v>
       </c>
       <c r="I59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L59" s="1" t="s">
         <v>1</v>
       </c>
@@ -6145,19 +6275,22 @@
         <v>1</v>
       </c>
       <c r="Q59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R59" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="R59" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6170,27 +6303,24 @@
       <c r="D60" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="K60" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L60" s="1" t="s">
         <v>1</v>
       </c>
@@ -6207,19 +6337,22 @@
         <v>1</v>
       </c>
       <c r="Q60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R60" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="R60" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6232,27 +6365,24 @@
       <c r="D61" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L61" s="1" t="s">
         <v>1</v>
       </c>
@@ -6269,19 +6399,22 @@
         <v>1</v>
       </c>
       <c r="Q61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R61" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="R61" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U61" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6294,27 +6427,24 @@
       <c r="D62" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L62" s="1" t="s">
         <v>1</v>
       </c>
@@ -6331,19 +6461,22 @@
         <v>1</v>
       </c>
       <c r="Q62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R62" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="R62" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6356,27 +6489,24 @@
       <c r="D63" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L63" s="1" t="s">
         <v>1</v>
       </c>
@@ -6393,19 +6523,22 @@
         <v>1</v>
       </c>
       <c r="Q63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R63" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="R63" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6418,27 +6551,24 @@
       <c r="D64" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L64" s="1" t="s">
         <v>1</v>
       </c>
@@ -6449,25 +6579,28 @@
         <v>1</v>
       </c>
       <c r="O64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P64" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="P64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S64" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="S64" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T64" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6480,18 +6613,15 @@
       <c r="D65" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I65" s="1" t="s">
         <v>1</v>
       </c>
@@ -6508,28 +6638,31 @@
         <v>1</v>
       </c>
       <c r="N65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O65" s="1" t="s">
+      <c r="P65" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="S65" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T65" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6542,24 +6675,21 @@
       <c r="D66" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K66" s="1" t="s">
         <v>1</v>
       </c>
@@ -6570,28 +6700,31 @@
         <v>1</v>
       </c>
       <c r="N66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="O66" s="1" t="s">
+      <c r="P66" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S66" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="S66" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T66" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6604,24 +6737,21 @@
       <c r="D67" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F67" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K67" s="1" t="s">
         <v>1</v>
       </c>
@@ -6635,25 +6765,28 @@
         <v>1</v>
       </c>
       <c r="O67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q67" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S67" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S67" s="1" t="s">
+      <c r="T67" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="T67" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U67" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6666,9 +6799,6 @@
       <c r="D68" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F68" s="1" t="s">
         <v>1</v>
       </c>
@@ -6676,20 +6806,20 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M68" s="1" t="s">
         <v>1</v>
       </c>
@@ -6697,25 +6827,28 @@
         <v>1</v>
       </c>
       <c r="O68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P68" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q68" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="S68" s="1" t="s">
+      <c r="T68" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="T68" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U68" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6728,9 +6861,6 @@
       <c r="D69" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F69" s="1" t="s">
         <v>1</v>
       </c>
@@ -6741,20 +6871,20 @@
         <v>1</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N69" s="1" t="s">
         <v>1</v>
       </c>
@@ -6765,19 +6895,22 @@
         <v>1</v>
       </c>
       <c r="Q69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R69" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="R69" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S69" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -6791,55 +6924,58 @@
         <v>579</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1</v>
+        <v>614</v>
       </c>
       <c r="F70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="N70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="P70" s="1" t="s">
+      <c r="Q70" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="Q70" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="S70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T70" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="T70" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U70" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -6852,9 +6988,6 @@
       <c r="D71" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F71" s="1" t="s">
         <v>1</v>
       </c>
@@ -6898,25 +7031,25 @@
         <v>1</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H72" s="1" t="s">
         <v>1</v>
       </c>
@@ -6939,52 +7072,52 @@
         <v>1</v>
       </c>
       <c r="O72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P72" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="P72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q72" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="S72" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T72" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H73" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="K73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L73" s="1" t="s">
         <v>1</v>
       </c>
@@ -6995,61 +7128,61 @@
         <v>1</v>
       </c>
       <c r="O73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P73" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="P73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q73" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S73" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S73" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T73" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="N74" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="N74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O74" s="1" t="s">
         <v>1</v>
       </c>
@@ -7060,49 +7193,49 @@
         <v>1</v>
       </c>
       <c r="R74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S74" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="S74" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T74" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M75" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N75" s="1" t="s">
         <v>1</v>
       </c>
@@ -7116,252 +7249,252 @@
         <v>1</v>
       </c>
       <c r="R75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S75" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="S75" s="1" t="s">
+      <c r="T75" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="T75" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U75" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="N76" s="1" t="s">
+      <c r="O76" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="O76" s="1" t="s">
+      <c r="P76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="P76" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S76" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="S76" s="1" t="s">
+      <c r="T76" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="T76" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U76" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="N77" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="O77" s="1" t="s">
+      <c r="P77" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="P77" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R77" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="R77" s="1" t="s">
+      <c r="S77" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="S77" s="1" t="s">
+      <c r="T77" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="T77" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U77" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="1" t="s">
         <v>229</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J78" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L78" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="O78" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="O78" s="1" t="s">
+      <c r="P78" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="P78" s="1" t="s">
+      <c r="Q78" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="Q78" s="1" t="s">
+      <c r="R78" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="R78" s="1" t="s">
+      <c r="S78" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="S78" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T78" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U78" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F79" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="N79" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="N79" s="1" t="s">
+      <c r="O79" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="O79" s="1" t="s">
+      <c r="P79" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="P79" s="1" t="s">
+      <c r="Q79" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="Q79" s="1" t="s">
+      <c r="R79" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="R79" s="1" t="s">
+      <c r="S79" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="S79" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T79" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U79" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>235</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G80" s="1" t="s">
         <v>1</v>
       </c>
@@ -7375,46 +7508,46 @@
         <v>1</v>
       </c>
       <c r="K80" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M80" s="1" t="s">
+      <c r="N80" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="O80" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="O80" s="1" t="s">
+      <c r="P80" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="P80" s="1" t="s">
+      <c r="Q80" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="Q80" s="1" t="s">
+      <c r="R80" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="R80" s="1" t="s">
+      <c r="S80" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="S80" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T80" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U80" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F81" s="1" t="s">
         <v>1</v>
       </c>
@@ -7458,19 +7591,19 @@
         <v>1</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U81" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F82" s="1" t="s">
         <v>1</v>
       </c>
@@ -7514,19 +7647,19 @@
         <v>1</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U82" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F83" s="1" t="s">
         <v>1</v>
       </c>
@@ -7570,10 +7703,13 @@
         <v>1</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U83" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>31</v>
       </c>
@@ -7581,7 +7717,7 @@
         <v>579</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1</v>
+        <v>621</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>1</v>
@@ -7602,20 +7738,20 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N84" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P84" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="P84" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q84" s="1" t="s">
         <v>1</v>
       </c>
@@ -7626,10 +7762,13 @@
         <v>1</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U84" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>32</v>
       </c>
@@ -7637,32 +7776,32 @@
         <v>579</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1</v>
+        <v>622</v>
       </c>
       <c r="F85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K85" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M85" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N85" s="1" t="s">
         <v>1</v>
       </c>
@@ -7682,19 +7821,19 @@
         <v>1</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U85" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F86" s="1" t="s">
         <v>1</v>
       </c>
@@ -7702,17 +7841,17 @@
         <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L86" s="1" t="s">
         <v>1</v>
       </c>
@@ -7720,46 +7859,46 @@
         <v>1</v>
       </c>
       <c r="N86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O86" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P86" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R86" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="R86" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S86" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U86" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F87" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I87" s="1" t="s">
         <v>1</v>
       </c>
@@ -7770,34 +7909,37 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M87" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O87" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="O87" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P87" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R87" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="R87" s="1" t="s">
+      <c r="S87" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="S87" s="1" t="s">
+      <c r="T87" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="T87" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U87" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>255</v>
       </c>
@@ -7805,7 +7947,7 @@
         <v>579</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1</v>
+        <v>629</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>1</v>
@@ -7817,43 +7959,46 @@
         <v>1</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K88" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M88" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O88" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="O88" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P88" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R88" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="R88" s="1" t="s">
+      <c r="S88" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="S88" s="1" t="s">
+      <c r="T88" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="T88" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U88" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
         <v>256</v>
       </c>
@@ -7861,55 +8006,58 @@
         <v>579</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1</v>
+        <v>630</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O89" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="O89" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P89" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R89" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="R89" s="1" t="s">
+      <c r="S89" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="S89" s="1" t="s">
+      <c r="T89" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="T89" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U89" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>257</v>
       </c>
@@ -7917,23 +8065,23 @@
         <v>579</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1</v>
+        <v>631</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I90" s="5" t="s">
+      <c r="I90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J90" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K90" s="1" t="s">
         <v>1</v>
       </c>
@@ -7944,46 +8092,46 @@
         <v>1</v>
       </c>
       <c r="N90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O90" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="O90" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="Q90" s="1" t="s">
+      <c r="R90" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="R90" s="1" t="s">
+      <c r="S90" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="S90" s="1" t="s">
+      <c r="T90" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="T90" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U90" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
         <v>258</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F91" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H91" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I91" s="1" t="s">
         <v>1</v>
       </c>
@@ -8009,37 +8157,37 @@
         <v>1</v>
       </c>
       <c r="Q91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R91" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="R91" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T91" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U91" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F92" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H92" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I92" s="1" t="s">
         <v>1</v>
       </c>
@@ -8065,28 +8213,28 @@
         <v>1</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="R92" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T92" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="T92" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U92" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>244</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F93" s="1" t="s">
         <v>1</v>
       </c>
@@ -8094,55 +8242,55 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L93" s="1" t="s">
+      <c r="M93" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N93" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P93" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="R93" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S93" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U93" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F94" s="1" t="s">
         <v>1</v>
       </c>
@@ -8156,49 +8304,49 @@
         <v>1</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="M94" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P94" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="P94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R94" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="R94" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U94" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F95" s="1" t="s">
         <v>1</v>
       </c>
@@ -8212,49 +8360,49 @@
         <v>1</v>
       </c>
       <c r="J95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K95" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M95" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="M95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P95" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="P95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R95" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="R95" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U95" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F96" s="1" t="s">
         <v>1</v>
       </c>
@@ -8262,55 +8410,55 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L96" s="1" t="s">
+      <c r="M96" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N96" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O96" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P96" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="P96" s="1" t="s">
+      <c r="Q96" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="Q96" s="1" t="s">
+      <c r="R96" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="R96" s="1" t="s">
+      <c r="S96" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="S96" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T96" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U96" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F97" s="1" t="s">
         <v>1</v>
       </c>
@@ -8327,55 +8475,55 @@
         <v>1</v>
       </c>
       <c r="K97" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N97" s="1" t="s">
         <v>1</v>
       </c>
       <c r="O97" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P97" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="P97" s="1" t="s">
+      <c r="Q97" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="Q97" s="1" t="s">
+      <c r="R97" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="R97" s="1" t="s">
+      <c r="S97" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="S97" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T97" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U97" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
         <v>260</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F98" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I98" s="1" t="s">
         <v>1</v>
       </c>
@@ -8395,34 +8543,34 @@
         <v>1</v>
       </c>
       <c r="O98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P98" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="P98" s="1" t="s">
+      <c r="Q98" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="Q98" s="1" t="s">
+      <c r="R98" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="R98" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S98" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T98" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="T98" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U98" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F99" s="1" t="s">
         <v>1</v>
       </c>
@@ -8451,96 +8599,96 @@
         <v>1</v>
       </c>
       <c r="O99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P99" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="P99" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R99" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="R99" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T99" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="T99" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U99" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J100" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M100" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O100" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="O100" s="1" t="s">
+      <c r="P100" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="P100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R100" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="R100" s="1" t="s">
+      <c r="S100" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="S100" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T100" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U100" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H101" s="1" t="s">
         <v>1</v>
       </c>
@@ -8548,55 +8696,55 @@
         <v>1</v>
       </c>
       <c r="J101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="L101" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M101" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="O101" s="1" t="s">
+      <c r="P101" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="P101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R101" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="R101" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S101" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H102" s="1" t="s">
         <v>1</v>
       </c>
@@ -8604,55 +8752,55 @@
         <v>1</v>
       </c>
       <c r="J102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K102" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="L102" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M102" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="O102" s="1" t="s">
+      <c r="P102" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="P102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q102" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R102" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="R102" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S102" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U102" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H103" s="1" t="s">
         <v>1</v>
       </c>
@@ -8660,67 +8808,67 @@
         <v>1</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="L103" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O103" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="O103" s="1" t="s">
+      <c r="P103" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="P103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R103" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="R103" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U103" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="H104" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="I104" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L104" s="1" t="s">
         <v>1</v>
       </c>
@@ -8731,52 +8879,52 @@
         <v>1</v>
       </c>
       <c r="O104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P104" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="P104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q104" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R104" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="R104" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S104" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U104" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L105" s="1" t="s">
         <v>1</v>
       </c>
@@ -8787,55 +8935,55 @@
         <v>1</v>
       </c>
       <c r="O105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P105" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="P105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q105" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R105" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="R105" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S105" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U105" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J106" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L106" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="L106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M106" s="1" t="s">
         <v>1</v>
       </c>
@@ -8843,34 +8991,34 @@
         <v>1</v>
       </c>
       <c r="O106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P106" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="P106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q106" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R106" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="R106" s="1" t="s">
+      <c r="S106" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="S106" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T106" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F107" s="1" t="s">
         <v>1</v>
       </c>
@@ -8878,11 +9026,11 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J107" s="1" t="s">
         <v>1</v>
       </c>
@@ -8899,34 +9047,34 @@
         <v>1</v>
       </c>
       <c r="O107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P107" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="P107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q107" s="1" t="s">
         <v>1</v>
       </c>
       <c r="R107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S107" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="S107" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T107" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F108" s="1" t="s">
         <v>1</v>
       </c>
@@ -8940,11 +9088,11 @@
         <v>1</v>
       </c>
       <c r="J108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K108" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L108" s="1" t="s">
         <v>1</v>
       </c>
@@ -8961,28 +9109,28 @@
         <v>1</v>
       </c>
       <c r="Q108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R108" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="R108" s="1" t="s">
+      <c r="S108" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="S108" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T108" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C109" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F109" s="1" t="s">
         <v>1</v>
       </c>
@@ -8993,11 +9141,11 @@
         <v>1</v>
       </c>
       <c r="I109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J109" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K109" s="1" t="s">
         <v>1</v>
       </c>
@@ -9014,22 +9162,25 @@
         <v>1</v>
       </c>
       <c r="P109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q109" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="Q109" s="1" t="s">
+      <c r="R109" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="R109" s="1" t="s">
+      <c r="S109" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="S109" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T109" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U109" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="1" t="s">
         <v>41</v>
       </c>
@@ -9037,7 +9188,7 @@
         <v>579</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1</v>
+        <v>615</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>1</v>
@@ -9052,11 +9203,11 @@
         <v>1</v>
       </c>
       <c r="J110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K110" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L110" s="1" t="s">
         <v>1</v>
       </c>
@@ -9064,28 +9215,31 @@
         <v>1</v>
       </c>
       <c r="N110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O110" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="O110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P110" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R110" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="R110" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S110" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U110" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="1" t="s">
         <v>42</v>
       </c>
@@ -9093,7 +9247,7 @@
         <v>579</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1</v>
+        <v>628</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>1</v>
@@ -9108,11 +9262,11 @@
         <v>1</v>
       </c>
       <c r="J111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L111" s="1" t="s">
         <v>1</v>
       </c>
@@ -9120,43 +9274,43 @@
         <v>1</v>
       </c>
       <c r="N111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O111" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="O111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="P111" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R111" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="R111" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S111" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U111" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C112" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G112" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H112" s="1" t="s">
         <v>1</v>
       </c>
@@ -9164,17 +9318,17 @@
         <v>1</v>
       </c>
       <c r="J112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="K112" s="1" t="s">
+      <c r="L112" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L112" s="1" t="s">
+      <c r="M112" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M112" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N112" s="1" t="s">
         <v>1</v>
       </c>
@@ -9185,52 +9339,52 @@
         <v>1</v>
       </c>
       <c r="Q112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R112" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="R112" s="1" t="s">
+      <c r="S112" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="S112" s="1" t="s">
+      <c r="T112" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="T112" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U112" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="1" t="s">
         <v>288</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J113" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K113" s="2" t="s">
+      <c r="K113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L113" s="1" t="s">
+      <c r="M113" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M113" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N113" s="1" t="s">
         <v>1</v>
       </c>
@@ -9244,31 +9398,31 @@
         <v>1</v>
       </c>
       <c r="R113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S113" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="S113" s="1" t="s">
+      <c r="T113" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="T113" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U113" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H114" s="1" t="s">
         <v>1</v>
       </c>
@@ -9276,17 +9430,17 @@
         <v>1</v>
       </c>
       <c r="J114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K114" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K114" s="2" t="s">
+      <c r="L114" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L114" s="1" t="s">
+      <c r="M114" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N114" s="1" t="s">
         <v>1</v>
       </c>
@@ -9297,43 +9451,43 @@
         <v>1</v>
       </c>
       <c r="Q114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R114" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="R114" s="1" t="s">
+      <c r="S114" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="S114" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T114" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U114" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="1" t="s">
         <v>292</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H115" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J115" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K115" s="1" t="s">
         <v>1</v>
       </c>
@@ -9353,46 +9507,46 @@
         <v>1</v>
       </c>
       <c r="Q115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R115" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="R115" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="S115" s="1" t="s">
         <v>1</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U115" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="1" t="s">
         <v>293</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J116" s="1" t="s">
+      <c r="K116" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="K116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L116" s="1" t="s">
         <v>1</v>
       </c>
@@ -9403,11 +9557,11 @@
         <v>1</v>
       </c>
       <c r="O116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P116" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="P116" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q116" s="1" t="s">
         <v>1</v>
       </c>
@@ -9418,19 +9572,19 @@
         <v>1</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U116" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="1" t="s">
         <v>277</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F117" s="1" t="s">
         <v>1</v>
       </c>
@@ -9444,11 +9598,11 @@
         <v>1</v>
       </c>
       <c r="J117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K117" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L117" s="1" t="s">
         <v>1</v>
       </c>
@@ -9465,28 +9619,28 @@
         <v>1</v>
       </c>
       <c r="Q117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R117" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="R117" s="1" t="s">
+      <c r="S117" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="S117" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T117" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U117" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F118" s="1" t="s">
         <v>1</v>
       </c>
@@ -9500,11 +9654,11 @@
         <v>1</v>
       </c>
       <c r="J118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K118" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L118" s="1" t="s">
         <v>1</v>
       </c>
@@ -9521,28 +9675,28 @@
         <v>1</v>
       </c>
       <c r="Q118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R118" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="R118" s="1" t="s">
+      <c r="S118" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="S118" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T118" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U118" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F119" s="1" t="s">
         <v>1</v>
       </c>
@@ -9556,11 +9710,11 @@
         <v>1</v>
       </c>
       <c r="J119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K119" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K119" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L119" s="1" t="s">
         <v>1</v>
       </c>
@@ -9577,28 +9731,28 @@
         <v>1</v>
       </c>
       <c r="Q119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R119" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="R119" s="1" t="s">
+      <c r="S119" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="S119" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T119" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U119" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="1" t="s">
         <v>280</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F120" s="1" t="s">
         <v>1</v>
       </c>
@@ -9612,20 +9766,20 @@
         <v>1</v>
       </c>
       <c r="J120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L120" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N120" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="N120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O120" s="1" t="s">
         <v>1</v>
       </c>
@@ -9633,28 +9787,28 @@
         <v>1</v>
       </c>
       <c r="Q120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R120" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="R120" s="1" t="s">
+      <c r="S120" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="S120" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T120" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U120" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F121" s="1" t="s">
         <v>1</v>
       </c>
@@ -9662,35 +9816,35 @@
         <v>1</v>
       </c>
       <c r="H121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I121" s="1" t="s">
+      <c r="J121" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J121" s="1" t="s">
+      <c r="K121" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N121" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="N121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="Q121" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="R121" s="1" t="s">
         <v>1</v>
       </c>
@@ -9698,19 +9852,19 @@
         <v>1</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U121" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="1" t="s">
         <v>282</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F122" s="1" t="s">
         <v>1</v>
       </c>
@@ -9718,55 +9872,55 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I122" s="1" t="s">
+      <c r="J122" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="K122" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="L122" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M122" s="4" t="s">
+      <c r="M122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N122" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="N122" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O122" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q122" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="Q122" s="1" t="s">
+      <c r="R122" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="R122" s="1" t="s">
+      <c r="S122" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="S122" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="T122" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U122" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="1" t="s">
         <v>283</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F123" s="1" t="s">
         <v>1</v>
       </c>
@@ -9777,23 +9931,23 @@
         <v>1</v>
       </c>
       <c r="I123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J123" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J123" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K123" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M123" s="4" t="s">
+      <c r="M123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N123" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="N123" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="O123" s="1" t="s">
         <v>1</v>
       </c>
@@ -9810,19 +9964,19 @@
         <v>1</v>
       </c>
       <c r="T123" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U123" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F124" s="1" t="s">
         <v>1</v>
       </c>
@@ -9836,17 +9990,17 @@
         <v>1</v>
       </c>
       <c r="J124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K124" s="2" t="s">
+      <c r="L124" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="L124" s="1" t="s">
+      <c r="M124" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M124" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="N124" s="1" t="s">
         <v>1</v>
       </c>
@@ -9857,28 +10011,28 @@
         <v>1</v>
       </c>
       <c r="Q124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R124" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="R124" s="1" t="s">
+      <c r="S124" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="S124" s="1" t="s">
+      <c r="T124" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="T124" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U124" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="1" t="s">
         <v>294</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F125" s="1" t="s">
         <v>1</v>
       </c>
@@ -9922,19 +10076,19 @@
         <v>1</v>
       </c>
       <c r="T125" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U125" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="1" t="s">
         <v>295</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F126" s="1" t="s">
         <v>1</v>
       </c>
@@ -9978,19 +10132,19 @@
         <v>1</v>
       </c>
       <c r="T126" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U126" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F127" s="1" t="s">
         <v>1</v>
       </c>
@@ -9998,11 +10152,11 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I127" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I127" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J127" s="1" t="s">
         <v>1</v>
       </c>
@@ -10034,19 +10188,19 @@
         <v>1</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U127" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="1" t="s">
         <v>299</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F128" s="1" t="s">
         <v>1</v>
       </c>
@@ -10057,14 +10211,14 @@
         <v>1</v>
       </c>
       <c r="I128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J128" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="K128" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="K128" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L128" s="1" t="s">
         <v>1</v>
       </c>
@@ -10075,11 +10229,11 @@
         <v>1</v>
       </c>
       <c r="O128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P128" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="P128" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q128" s="1" t="s">
         <v>1</v>
       </c>
@@ -10090,19 +10244,19 @@
         <v>1</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U128" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="1" t="s">
         <v>300</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F129" s="1" t="s">
         <v>1</v>
       </c>
@@ -10113,11 +10267,11 @@
         <v>1</v>
       </c>
       <c r="I129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J129" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J129" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="K129" s="1" t="s">
         <v>1</v>
       </c>
@@ -10131,11 +10285,11 @@
         <v>1</v>
       </c>
       <c r="O129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P129" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="P129" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q129" s="1" t="s">
         <v>1</v>
       </c>
@@ -10146,19 +10300,19 @@
         <v>1</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U129" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="1" t="s">
         <v>301</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F130" s="1" t="s">
         <v>1</v>
       </c>
@@ -10169,14 +10323,14 @@
         <v>1</v>
       </c>
       <c r="I130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J130" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J130" s="1" t="s">
+      <c r="K130" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="K130" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L130" s="1" t="s">
         <v>1</v>
       </c>
@@ -10187,11 +10341,11 @@
         <v>1</v>
       </c>
       <c r="O130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P130" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="P130" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q130" s="1" t="s">
         <v>1</v>
       </c>
@@ -10202,19 +10356,19 @@
         <v>1</v>
       </c>
       <c r="T130" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U130" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="1" t="s">
         <v>302</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F131" s="1" t="s">
         <v>1</v>
       </c>
@@ -10225,14 +10379,14 @@
         <v>1</v>
       </c>
       <c r="I131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J131" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J131" s="1" t="s">
+      <c r="K131" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K131" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L131" s="1" t="s">
         <v>1</v>
       </c>
@@ -10243,11 +10397,11 @@
         <v>1</v>
       </c>
       <c r="O131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P131" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="P131" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q131" s="1" t="s">
         <v>1</v>
       </c>
@@ -10258,19 +10412,19 @@
         <v>1</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U131" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="1" t="s">
         <v>303</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F132" s="1" t="s">
         <v>1</v>
       </c>
@@ -10281,14 +10435,14 @@
         <v>1</v>
       </c>
       <c r="I132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J132" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J132" s="1" t="s">
+      <c r="K132" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K132" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L132" s="1" t="s">
         <v>1</v>
       </c>
@@ -10299,11 +10453,11 @@
         <v>1</v>
       </c>
       <c r="O132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P132" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="P132" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q132" s="1" t="s">
         <v>1</v>
       </c>
@@ -10314,19 +10468,19 @@
         <v>1</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U132" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="1" t="s">
         <v>304</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F133" s="1" t="s">
         <v>1</v>
       </c>
@@ -10337,14 +10491,14 @@
         <v>1</v>
       </c>
       <c r="I133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J133" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J133" s="1" t="s">
+      <c r="K133" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="K133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L133" s="1" t="s">
         <v>1</v>
       </c>
@@ -10355,11 +10509,11 @@
         <v>1</v>
       </c>
       <c r="O133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P133" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="P133" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q133" s="1" t="s">
         <v>1</v>
       </c>
@@ -10370,37 +10524,37 @@
         <v>1</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U133" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="1" t="s">
         <v>311</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F134" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="L134" s="1" t="s">
         <v>1</v>
       </c>
@@ -10411,11 +10565,11 @@
         <v>1</v>
       </c>
       <c r="O134" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P134" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="P134" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q134" s="1" t="s">
         <v>1</v>
       </c>
@@ -10426,19 +10580,19 @@
         <v>1</v>
       </c>
       <c r="T134" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="135" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U134" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C135" s="1" t="s">
         <v>312</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F135" s="1" t="s">
         <v>1</v>
       </c>
@@ -10452,14 +10606,14 @@
         <v>1</v>
       </c>
       <c r="J135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K135" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K135" s="1" t="s">
+      <c r="L135" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="L135" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M135" s="1" t="s">
         <v>1</v>
       </c>
@@ -10467,11 +10621,11 @@
         <v>1</v>
       </c>
       <c r="O135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P135" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="P135" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q135" s="1" t="s">
         <v>1</v>
       </c>
@@ -10482,19 +10636,19 @@
         <v>1</v>
       </c>
       <c r="T135" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U135" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="1" t="s">
         <v>314</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F136" s="1" t="s">
         <v>1</v>
       </c>
@@ -10502,20 +10656,20 @@
         <v>1</v>
       </c>
       <c r="H136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I136" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K136" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K136" s="1" t="s">
+      <c r="L136" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="L136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M136" s="1" t="s">
         <v>1</v>
       </c>
@@ -10523,11 +10677,11 @@
         <v>1</v>
       </c>
       <c r="O136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P136" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="P136" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q136" s="1" t="s">
         <v>1</v>
       </c>
@@ -10538,19 +10692,19 @@
         <v>1</v>
       </c>
       <c r="T136" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="U136" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="1" t="s">
         <v>316</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="F137" s="1" t="s">
         <v>1</v>
       </c>
@@ -10558,20 +10712,20 @@
         <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I137" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="J137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K137" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K137" s="1" t="s">
+      <c r="L137" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="M137" s="1" t="s">
         <v>1</v>
       </c>
@@ -10579,11 +10733,11 @@
         <v>1</v>
       </c>
       <c r="O137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P137" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="P137" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="Q137" s="1" t="s">
         <v>1</v>
       </c>
@@ -10594,56 +10748,59 @@
         <v>1</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="138" spans="3:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E138" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U137" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="3:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F138" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="G138" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G138" s="1" t="s">
+      <c r="H138" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="J138" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J138" s="1" t="s">
+      <c r="K138" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="L138" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L138" s="1" t="s">
+      <c r="M138" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M138" s="1" t="s">
+      <c r="N138" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="N138" s="1" t="s">
+      <c r="O138" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="O138" s="1" t="s">
+      <c r="P138" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="P138" s="1" t="s">
+      <c r="Q138" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="Q138" s="1" t="s">
+      <c r="R138" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="R138" s="1" t="s">
+      <c r="S138" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="S138" s="1" t="s">
+      <c r="T138" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="T138" s="1" t="s">
+      <c r="U138" s="1" t="s">
         <v>7</v>
       </c>
     </row>
